--- a/stories/arbres/ATOM-REL.PAR.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche. Maman dit : on peut attendre. Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir. Maman dit : puis mon tour. Simon dit : puis mon tour. Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant. Maman dit : on attend. Puis mon tour arrive.</t>
+          <t>Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche. On peut attendre. Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir. Puis mon tour. Puis mon tour. Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant. On attend. Puis mon tour arrive.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche.
+maman|On peut attendre.
+narrateur|Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir.
+maman|Puis mon tour.
+enfant-m|Puis mon tour.
+narrateur|Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant.
+maman|On attend.
+narrateur|Puis mon tour arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila arrose. Que fait Simon ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Simon a su attendre. Puis mon tour est venu. Il a arrosé. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Simon pose l'arrosoir. Il prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Puis mon tour arrive.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Lila arrose. Que fait Simon ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Simon a su attendre. Puis mon tour est venu. Il a arrosé. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Simon pose l'arrosoir. Il prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Simon attend l'arrosoir</t>
+          <t>Aniss attend l'arrosoir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.PAR.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte tombe de l'arrosoir vert. Mila arrose les tomates. Aniss attend. Puis c'est son tour d'arroser une feuille.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche. On peut attendre. Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir. Puis mon tour. Puis mon tour. Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant. On attend. Puis mon tour arrive.</t>
+          <t>Les tomates pendent comme de petites lanternes. Elles sont rouges, un peu chaudes. Une goutte tombe de l'arrosoir vert. Elle fait un rond dans la terre. La maison est juste derrière les haricots. Aniss habite ici, avec maman. Papa coupe le thym, plus loin. Ça sent la terre mouillée. Une abeille passe tout près d'une fleur. Tu as vu la goutte, Aniss ? Elle a fait un rond, maman. Viens. On va près des tomates. Le thym sent fort, un peu piquant. Papa coupe le thym, tu l'as vu ? Oui, maman. Un seau bleu dort sous les haricots. Le seau est vide, hein ? Oui. En ce moment, le jardin est calme. Mila tient déjà l'arrosoir. Elle arrose les tomates, tout doux. L'eau chante sur les feuilles. Aniss a envie de l'arrosoir. Maman, je veux arroser. On peut attendre. Mila finit son tour. Puis c'est le tien. Aniss pose les pieds au sol. Il sent l'eau qui tombe. Maman tient sa main. Mila arrose encore une feuille. Tu attends bien, Aniss. Tes pieds restent au sol. Bravo. Une tomate brille au soleil. Elle est bien rouge, hein ? Oui, maman. L'arrosoir est encore un peu lourd. Aniss attend. On reste près. Puis ce sera ton tour. Mila verse une dernière goutte. Aniss compte tout bas. Un. Deux. Trois. La terre devient sombre et douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1329,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche.
+          <t>narrateur|Les tomates pendent comme de petites lanternes.
+narrateur|Elles sont rouges, un peu chaudes.
+narrateur|Une goutte tombe de l'arrosoir vert.
+narrateur|Elle fait un rond dans la terre.
+narrateur|La maison est juste derrière les haricots.
+narrateur|Aniss habite ici, avec maman.
+narrateur|Papa coupe le thym, plus loin.
+narrateur|Ça sent la terre mouillée.
+narrateur|Une abeille passe tout près d'une fleur.
+maman|Tu as vu la goutte, Aniss ?
+enfant-m|Elle a fait un rond, maman.
+maman|Viens.
+maman|On va près des tomates.
+narrateur|Le thym sent fort, un peu piquant.
+maman|Papa coupe le thym, tu l'as vu ?
+enfant-m|Oui, maman.
+narrateur|Un seau bleu dort sous les haricots.
+maman|Le seau est vide, hein ?
+enfant-m|Oui.
+narrateur|En ce moment, le jardin est calme.
+narrateur|Mila tient déjà l'arrosoir.
+narrateur|Elle arrose les tomates, tout doux.
+narrateur|L'eau chante sur les feuilles.
+narrateur|Aniss a envie de l'arrosoir.
+enfant-m|Maman, je veux arroser.
 maman|On peut attendre.
-narrateur|Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir.
-maman|Puis mon tour.
-enfant-m|Puis mon tour.
-narrateur|Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant.
-maman|On attend.
-narrateur|Puis mon tour arrive.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Mila finit son tour.
+maman|Puis c'est le tien.
+narrateur|Aniss pose les pieds au sol.
+narrateur|Il sent l'eau qui tombe.
+narrateur|Maman tient sa main.
+narrateur|Mila arrose encore une feuille.
+maman|Tu attends bien, Aniss.
+maman|Tes pieds restent au sol.
+maman|Bravo.
+narrateur|Une tomate brille au soleil.
+maman|Elle est bien rouge, hein ?
+enfant-m|Oui, maman.
+narrateur|L'arrosoir est encore un peu lourd.
+narrateur|Aniss attend.
+maman|On reste près.
+maman|Puis ce sera ton tour.
+narrateur|Mila verse une dernière goutte.
+narrateur|Aniss compte tout bas.
+enfant-m|Un.
+enfant-m|Deux.
+enfant-m|Trois.
+narrateur|La terre devient sombre et douce.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila arrose. Que fait Simon ?</t>
+          <t>Mila arrose. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1564,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila arrose. Que fait Simon ?</t>
+          <t>narrateur|Mila arrose.
+narrateur|Que fait Aniss ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Simon a su attendre. Puis mon tour est venu. Il a arrosé. Maman est là.</t>
+          <t>Mila pose l'arrosoir. Maintenant. Puis c'est ton tour. Puis mon tour. Aniss prend l'arrosoir. L'eau est fraîche contre ses mains. Il arrose une feuille. La feuille tremble un peu. Bravo, Aniss. Tu as attendu. C'est du bon travail. L'eau est froide, maman. Oui. Elle est fraîche. Mila attend maintenant, près des tomates. Parce que tu as attendu, c'est ton tour. Une autre goutte fait un rond. Tu arroses tout doux, c'est bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1737,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Simon a su attendre. Puis mon tour est venu. Il a arrosé. Maman est là.</t>
+          <t>narrateur|Mila pose l'arrosoir.
+maman|Maintenant.
+maman|Puis c'est ton tour.
+enfant-m|Puis mon tour.
+narrateur|Aniss prend l'arrosoir.
+narrateur|L'eau est fraîche contre ses mains.
+narrateur|Il arrose une feuille.
+narrateur|La feuille tremble un peu.
+maman|Bravo, Aniss.
+maman|Tu as attendu.
+maman|C'est du bon travail.
+enfant-m|L'eau est froide, maman.
+maman|Oui.
+maman|Elle est fraîche.
+narrateur|Mila attend maintenant, près des tomates.
+maman|Parce que tu as attendu, c'est ton tour.
+narrateur|Une autre goutte fait un rond.
+maman|Tu arroses tout doux, c'est bien.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Simon pose l'arrosoir. Il prend la main de maman.</t>
+          <t>Aniss pose l'arrosoir. Tu veux le laisser à Mila ? Oui, maman. Bravo. On peut prêter. Mila reprend l'arrosoir. Elle arrose une dernière tomate. Aniss prend la main de maman. On rentre boire un peu d'eau ? Oui. Les tomates brillent encore. La terre est sombre et douce. Tu as bien attendu, Aniss. Puis c'était mon tour. Oui. Puis ton tour. L'abeille est partie plus loin. Le jardin a eu de l'eau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1922,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Simon pose l'arrosoir. Il prend la main de maman.</t>
+          <t>narrateur|Aniss pose l'arrosoir.
+maman|Tu veux le laisser à Mila ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On peut prêter.
+narrateur|Mila reprend l'arrosoir.
+narrateur|Elle arrose une dernière tomate.
+narrateur|Aniss prend la main de maman.
+maman|On rentre boire un peu d'eau ?
+enfant-m|Oui.
+narrateur|Les tomates brillent encore.
+narrateur|La terre est sombre et douce.
+maman|Tu as bien attendu, Aniss.
+enfant-m|Puis c'était mon tour.
+maman|Oui.
+maman|Puis ton tour.
+narrateur|L'abeille est partie plus loin.
+maman|Le jardin a eu de l'eau.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai arrosé. Bravo, Aniss. Tu as fait du bon travail. L'arrosoir vert reste près des tomates. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2107,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai arrosé.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'arrosoir vert reste près des tomates.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-05.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Simon est au jardin avec maman. Lila arrose les tomates. L'arrosoir est vert. Simon a envie. Il s'approche. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Simon pose les pieds au sol. Il sent l'eau qui tombe. Lila arrose encore. Simon attend. Maman tient sa main. Lila pose l'arrosoir. Maman dit : puis mon tour. Simon dit : puis mon tour. Simon prend l'arrosoir. L'eau est fraîche. Il arrose une feuille. Lila attend maintenant. Maman dit : on attend. Puis mon tour arrive.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les tomates pendent comme de petites lanternes. Elles sont rouges, un peu chaudes. Une goutte tombe de l'arrosoir vert. Elle fait un rond dans la terre. La maison est juste derrière les haricots. Aniss habite ici, avec maman. Papa coupe le thym, plus loin. Ça sent la terre mouillée. Une abeille passe tout près d'une fleur. Tu as vu la goutte, Aniss ? Elle a fait un rond, maman. Viens. On va près des tomates. Le thym sent fort, un peu piquant. Papa coupe le thym, tu l'as vu ? Oui, maman. Un seau bleu dort sous les haricots. Le seau est vide, hein ? Oui. En ce moment, le jardin est calme. Mila tient déjà l'arrosoir. Elle arrose les tomates, tout doux. L'eau chante sur les feuilles. Aniss a envie de l'arrosoir. Maman, je veux arroser. On peut attendre. Mila finit son tour. Puis c'est le tien. Aniss pose les pieds au sol. Il sent l'eau qui tombe. Maman tient sa main. Mila arrose encore une feuille. Tu attends bien, Aniss. Tes pieds restent au sol. Bravo. Une tomate brille au soleil. Elle est bien rouge, hein ? Oui, maman. L'arrosoir est encore un peu lourd. Aniss attend. On reste près. Puis ce sera ton tour. Mila verse une dernière goutte. Aniss compte tout bas. Un. Deux. Trois. La terre devient sombre et douce.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila arrose. Que fait Simon ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila arrose. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1568,6 @@
 narrateur|Que fait Aniss ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila pose l'arrosoir. Maintenant. Puis c'est ton tour. Puis mon tour. Aniss prend l'arrosoir. L'eau est fraîche contre ses mains. Il arrose une feuille. La feuille tremble un peu. Bravo, Aniss. Tu as attendu. C'est du bon travail. L'eau est froide, maman. Oui. Elle est fraîche. Mila attend maintenant, près des tomates. Parce que tu as attendu, c'est ton tour. Une autre goutte fait un rond. Tu arroses tout doux, c'est bien.</t>
+          <t>Mila pose l'arrosoir. Maintenant. Puis c'est ton tour. Puis mon tour. Aniss prend l'arrosoir. L'eau est fraîche contre ses mains. Il arrose une feuille. La feuille tremble un peu. Bravo, Aniss. Tu as attendu. L'eau est froide, maman. Oui. Elle est fraîche. Mila attend maintenant, près des tomates. Parce que tu as attendu, c'est ton tour. Une autre goutte fait un rond. Tu arroses tout doux, c'est bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Simon a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Puis mon tour est venu. Il a arrosé. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila pose l'arrosoir. Maintenant. Puis c'est ton tour. Puis mon tour. Aniss prend l'arrosoir. L'eau est fraîche contre ses mains. Il arrose une feuille. La feuille tremble un peu. Bravo, Aniss. Tu as attendu. L'eau est froide, maman. Oui. Elle est fraîche. Mila attend maintenant, près des tomates. Parce que tu as attendu, c'est ton tour. Une autre goutte fait un rond. Tu arroses tout doux, c'est bien.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,7 +1746,6 @@
 narrateur|La feuille tremble un peu.
 maman|Bravo, Aniss.
 maman|Tu as attendu.
-maman|C'est du bon travail.
 enfant-m|L'eau est froide, maman.
 maman|Oui.
 maman|Elle est fraîche.
@@ -1757,7 +1755,6 @@
 maman|Tu arroses tout doux, c'est bien.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Simon pose l'arrosoir. Il prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose l'arrosoir. Tu veux le laisser à Mila ? Oui, maman. Bravo. On peut prêter. Mila reprend l'arrosoir. Elle arrose une dernière tomate. Aniss prend la main de maman. On rentre boire un peu d'eau ? Oui. Les tomates brillent encore. La terre est sombre et douce. Tu as bien attendu, Aniss. Puis c'était mon tour. Oui. Puis ton tour. L'abeille est partie plus loin. Le jardin a eu de l'eau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1939,6 @@
 maman|Le jardin a eu de l'eau.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis j'ai arrosé. Bravo, Aniss. Tu as fait du bon travail. L'arrosoir vert reste près des tomates. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai arrosé. Bravo, Aniss. L'arrosoir vert reste près des tomates.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis j'ai arrosé. Bravo, Aniss. L'arrosoir vert reste près des tomates.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,12 +2106,9 @@
           <t>enfant-m|J'ai attendu.
 enfant-m|Puis j'ai arrosé.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
-narrateur|L'arrosoir vert reste près des tomates.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'arrosoir vert reste près des tomates.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2134,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simon, Lila, maman</t>
+          <t>Aniss, Mila, maman</t>
         </is>
       </c>
     </row>
